--- a/report/methods_description_track1.xlsx
+++ b/report/methods_description_track1.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Anthropic, Claude (Sonnet 5), via Claude Code (agentic CLI), commercial subscription; Anthropic states Claude Code / API traffic is not used for model training. Claude designed and executed the analysis scripts, interpreted outputs and drafted the report under human direction. Data handling: all controlled-access files (FASTQ, VCF) were processed only by scripts running on the local machine and were never uploaded to Anthropic. Portions of derived, aggregate results and a limited number of individual VCF lines passed through the model's context during the interactive coding session.</t>
+          <t>Anthropic, Claude (Sonnet 5), via Claude Code (agentic CLI), on a Claude Pro plan (Anthropic consumer terms). CORRECTION (October 2026): the submitted version of this field said "commercial subscription; Anthropic states Claude Code / API traffic is not used for model training". That was wrong: the account's model-training setting ("Help improve Claude") was on during this work. We found it on 7 October 2026 and switched it off the same day; no feedback was ever given on outputs; the incident was self-reported to Sage's Privacy, Security &amp; Compliance Office, and on 9 October 2026 we requested permanent deletion of Anthropic's server-side copies of the sessions. Claude designed and executed the analysis scripts, interpreted outputs and drafted the report under human direction. Data handling: all controlled-access files (FASTQ, VCF) were processed only by scripts running on the local machine and were never uploaded to Anthropic. Portions of derived, aggregate results and a limited number of individual VCF lines passed through the model's context during the interactive coding session.</t>
         </is>
       </c>
     </row>
